--- a/Training_Tracker.xlsx
+++ b/Training_Tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
   <si>
     <t>📅 Start Date</t>
   </si>
@@ -58,67 +58,28 @@
     <t>2026-03-16</t>
   </si>
   <si>
-    <t>Host</t>
-  </si>
-  <si>
-    <t>asd</t>
-  </si>
-  <si>
-    <t>sad</t>
+    <t>Invitational</t>
+  </si>
+  <si>
+    <t>iop</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>Under review</t>
-  </si>
-  <si>
-    <t>cxvcxv</t>
+    <t>ioppo</t>
+  </si>
+  <si>
+    <t>Implemented</t>
+  </si>
+  <si>
+    <t>ipoi</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Participant</t>
-  </si>
-  <si>
-    <t>hjkhj</t>
-  </si>
-  <si>
-    <t>khjkhj</t>
-  </si>
-  <si>
-    <t>jhkh</t>
-  </si>
-  <si>
-    <t>Suspended</t>
-  </si>
-  <si>
-    <t>khjk</t>
-  </si>
-  <si>
-    <t>jkhj</t>
-  </si>
-  <si>
-    <t>hjkhjk</t>
-  </si>
-  <si>
-    <t>khjkhjk</t>
-  </si>
-  <si>
-    <t>Invitational</t>
-  </si>
-  <si>
-    <t>iop</t>
-  </si>
-  <si>
-    <t>ioppo</t>
-  </si>
-  <si>
-    <t>Implemented</t>
-  </si>
-  <si>
-    <t>ipoi</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>bnmbnm</t>
@@ -159,6 +120,9 @@
     <t>inn</t>
   </si>
   <si>
+    <t>Under review</t>
+  </si>
+  <si>
     <t>Status Update</t>
   </si>
   <si>
@@ -166,6 +130,9 @@
   </si>
   <si>
     <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>Host</t>
   </si>
   <si>
     <t>BDRRMC Rescue Volunteers, Tres De Mayo Digos City</t>
@@ -627,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
@@ -700,13 +667,13 @@
         <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>19</v>
@@ -721,10 +688,10 @@
         <v>16</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="4" t="s">
         <v>20</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -735,28 +702,28 @@
         <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>27</v>
@@ -765,10 +732,10 @@
         <v>28</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -776,183 +743,95 @@
         <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>49</v>
+      <c r="M5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2:C7">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2:C5">
       <formula1>"Invitational,Host,Participant,All"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2:I7">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2:I5">
       <formula1>"Implemented,In progress,Under review,Suspended,Paused"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Training_Tracker.xlsx
+++ b/Training_Tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>📅 Start Date</t>
   </si>
@@ -58,49 +58,10 @@
     <t>2026-03-16</t>
   </si>
   <si>
-    <t>Invitational</t>
-  </si>
-  <si>
-    <t>iop</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>ioppo</t>
-  </si>
-  <si>
-    <t>Implemented</t>
-  </si>
-  <si>
-    <t>ipoi</t>
-  </si>
-  <si>
-    <t/>
+    <t>2026-03-31</t>
   </si>
   <si>
     <t>Participant</t>
-  </si>
-  <si>
-    <t>bnmbnm</t>
-  </si>
-  <si>
-    <t>bnmnbm</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>Paused</t>
-  </si>
-  <si>
-    <t>bnmbn</t>
-  </si>
-  <si>
-    <t>bnm</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
   </si>
   <si>
     <t>capitol lobby</t>
@@ -155,7 +116,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -167,10 +128,6 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
       <u/>
@@ -238,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -250,9 +207,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -594,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
@@ -655,183 +609,95 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2:C5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2:C3">
       <formula1>"Invitational,Host,Participant,All"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2:I5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2:I3">
       <formula1>"Implemented,In progress,Under review,Suspended,Paused"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Training_Tracker.xlsx
+++ b/Training_Tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>📅 Start Date</t>
   </si>
@@ -28,7 +28,10 @@
     <t>🔤 Activity</t>
   </si>
   <si>
-    <t>👥 Instructor / Participants</t>
+    <t>👨‍🏫 Instructors</t>
+  </si>
+  <si>
+    <t>👥 Participants</t>
   </si>
   <si>
     <t>🔢 Pax</t>
@@ -548,19 +551,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="6" width="45" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="14" width="20" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,30 +608,33 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -636,60 +644,66 @@
         <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="N2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="N3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Training_Tracker.xlsx
+++ b/Training_Tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>📅 Start Date</t>
   </si>
@@ -58,48 +58,16 @@
     <t>📊 Reports</t>
   </si>
   <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>Participant</t>
-  </si>
-  <si>
-    <t>capitol lobby</t>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>Host</t>
+  </si>
+  <si>
+    <t>BDRRMC Rescue Volunteers, Tres De Mayo Digos City</t>
   </si>
   <si>
     <t>Basic Rescue And Life Support Training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. roel
-2. paul
-3. ortiz</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>inn</t>
-  </si>
-  <si>
-    <t>Under review</t>
-  </si>
-  <si>
-    <t>Status Update</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/document/d/1m7LabZ5YpCC5ukBVdWbcoz1a3mu6QFWG/edit?usp=sharing&amp;ouid=105207499158180641942&amp;rtpof=true&amp;sd=true</t>
-  </si>
-  <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>Host</t>
-  </si>
-  <si>
-    <t>BDRRMC Rescue Volunteers, Tres De Mayo Digos City</t>
   </si>
   <si>
     <t xml:space="preserve">1. kert
@@ -113,6 +81,15 @@
   </si>
   <si>
     <t>Santolan Gymnasium, Emily Homes Digos City</t>
+  </si>
+  <si>
+    <t>Under review</t>
+  </si>
+  <si>
+    <t>Status Update</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1m7LabZ5YpCC5ukBVdWbcoz1a3mu6QFWG/edit?usp=sharing&amp;ouid=105207499158180641942&amp;rtpof=true&amp;sd=true</t>
   </si>
 </sst>
 </file>
@@ -551,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
@@ -617,101 +594,54 @@
         <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="O2" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2:C3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2">
       <formula1>"Invitational,Host,Participant,All"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2:I3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2">
       <formula1>"Implemented,In progress,Under review,Suspended,Paused"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Training_Tracker.xlsx
+++ b/Training_Tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>📅 Start Date</t>
   </si>
@@ -58,10 +58,46 @@
     <t>📊 Reports</t>
   </si>
   <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>Host</t>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>Participant</t>
+  </si>
+  <si>
+    <t>likod capitol</t>
+  </si>
+  <si>
+    <t>zxczxc</t>
+  </si>
+  <si>
+    <t>zxcxzc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. zxczxczx
+2. zxczxc
+3. zxcz
+4. cx</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Santolan Gymnasium, Emily Homes Digos City</t>
+  </si>
+  <si>
+    <t>Under review</t>
+  </si>
+  <si>
+    <t>Status Update</t>
+  </si>
+  <si>
+    <t>zxc</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>All</t>
   </si>
   <si>
     <t>BDRRMC Rescue Volunteers, Tres De Mayo Digos City</t>
@@ -70,26 +106,16 @@
     <t>Basic Rescue And Life Support Training</t>
   </si>
   <si>
-    <t xml:space="preserve">1. kert
-2. paul
-3. roel
-4. brent
-5. kertty</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Santolan Gymnasium, Emily Homes Digos City</t>
-  </si>
-  <si>
-    <t>Under review</t>
-  </si>
-  <si>
-    <t>Status Update</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/document/d/1m7LabZ5YpCC5ukBVdWbcoz1a3mu6QFWG/edit?usp=sharing&amp;ouid=105207499158180641942&amp;rtpof=true&amp;sd=true</t>
+    <t>asdasd</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>asdsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> dsadsa</t>
   </si>
 </sst>
 </file>
@@ -110,8 +136,7 @@
       <sz val="11"/>
     </font>
     <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -528,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
@@ -609,39 +634,86 @@
         <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="L3" s="2" t="s">
         <v>24</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2:C3">
       <formula1>"Invitational,Host,Participant,All"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2:I3">
       <formula1>"Implemented,In progress,Under review,Suspended,Paused"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Training_Tracker.xlsx
+++ b/Training_Tracker.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Training Tracker" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Training Received Letters" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="57">
   <si>
     <t>📅 Start Date</t>
   </si>
@@ -56,6 +57,27 @@
   </si>
   <si>
     <t>📊 Reports</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>Host</t>
+  </si>
+  <si>
+    <t>asd</t>
+  </si>
+  <si>
+    <t>sad</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>ads</t>
   </si>
   <si>
     <t>2026-03-26</t>
@@ -116,6 +138,56 @@
   </si>
   <si>
     <t xml:space="preserve"> dsadsa</t>
+  </si>
+  <si>
+    <t>📅 Received Date</t>
+  </si>
+  <si>
+    <t>📅 Date of Activity</t>
+  </si>
+  <si>
+    <t>🔘 Type of Activity</t>
+  </si>
+  <si>
+    <t>👨‍🏫 Instructor / Participants</t>
+  </si>
+  <si>
+    <t>🔢 No. of Pax</t>
+  </si>
+  <si>
+    <t>📝 Actioned Communication</t>
+  </si>
+  <si>
+    <t>📝 Remarks from Admin &amp; Training Head</t>
+  </si>
+  <si>
+    <t>📝 Remarks from Training Unit</t>
+  </si>
+  <si>
+    <t>💬 Response Remarks from Training Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hgkhgkjhg
+hgkjgkj
+kghkh</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>asdas</t>
+  </si>
+  <si>
+    <t>hjg</t>
+  </si>
+  <si>
+    <t>dsfds</t>
+  </si>
+  <si>
+    <t>Canceled</t>
+  </si>
+  <si>
+    <t>sdffdg</t>
   </si>
 </sst>
 </file>
@@ -553,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="15" customWidth="1"/>
@@ -628,96 +700,250 @@
         <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="O2" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>30</v>
+      <c r="L4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2:C3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the list." sqref="C2:C4">
       <formula1>"Invitational,Host,Participant,All"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2:I3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Status" error="Please select a valid status." sqref="I2:I4">
       <formula1>"Implemented,In progress,Under review,Suspended,Paused"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="11" width="35" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>